--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,642 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131288327</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137357420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106431</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137357420</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137359310</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106591</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137359310</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137357328</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107932</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221705</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ängskovall</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137357328</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137358519</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100064</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137358519</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137358327</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99682</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137358327</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137357383</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99714</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>700 m O Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>394109</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6225660</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraövervakning Skåne Millora 2.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137357383</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1692,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106431</v>
+        <v>106436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107932</v>
+        <v>107937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100064</v>
+        <v>100069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99714</v>
+        <v>99719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106436</v>
+        <v>106439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107937</v>
+        <v>107940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99719</v>
+        <v>99722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106439</v>
+        <v>106445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107940</v>
+        <v>107946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99722</v>
+        <v>99728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106445</v>
+        <v>106446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107946</v>
+        <v>107947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106446</v>
+        <v>106458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107947</v>
+        <v>107959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99728</v>
+        <v>99740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106458</v>
+        <v>106459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107959</v>
+        <v>107960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99740</v>
+        <v>99741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106459</v>
+        <v>106462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107960</v>
+        <v>107963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100091</v>
+        <v>100094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99741</v>
+        <v>99744</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 6890-2026 artfynd.xlsx
+++ b/artfynd/A 6890-2026 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>137357420</v>
       </c>
       <c r="B5" t="n">
-        <v>106462</v>
+        <v>106468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137359310</v>
       </c>
       <c r="B6" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137357328</v>
       </c>
       <c r="B7" t="n">
-        <v>107963</v>
+        <v>107969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137358519</v>
       </c>
       <c r="B8" t="n">
-        <v>100094</v>
+        <v>100098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137358327</v>
       </c>
       <c r="B9" t="n">
-        <v>99712</v>
+        <v>99716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>137357383</v>
       </c>
       <c r="B10" t="n">
-        <v>99744</v>
+        <v>99748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
